--- a/plantillas/14.xlsx
+++ b/plantillas/14.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$3</definedName>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/14.xlsx
+++ b/plantillas/14.xlsx
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/14.xlsx
+++ b/plantillas/14.xlsx
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
